--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,276 +571,280 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-M-2PC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa  and  Loveseat Manual</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MICAELIS Sofa  and  Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.
-Product Dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22")
+MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
 Size: Black [NOT AVAILABLE]
 Features
 - Recliners
 - Sinious Spring and Webbing Suspension
 - Pillow Top Arms
 - 2.0 LB High Density Foam w/ Pocketed Coil Springs
-- FSC Certified
-Included items and dimensions:
+- FSC Certified Included items and dimensions:
 - Black [NOT AVAILABLE] Sofa: color: Black; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional
 - Black [NOT AVAILABLE] Loveseat: color: Black; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Black
 Weight: 372.58 lbs</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa  and  Loveseat Manual Black [NOT AVAILABLE] | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual Black [NOT AVAILABLE] | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Sofa + Loveseat Manual, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-SF-M, FM69007BK-LV-M</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="1" t="n">
         <v>372.58</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="Z2" s="1" t="n"/>
+      <c r="AA2" s="1" t="n"/>
+      <c r="AB2" s="1" t="n"/>
+      <c r="AC2" s="1" t="n">
         <v>58.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Slate Blue</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-M-2PC</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa  and  Loveseat Manual</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>FREE SHIPPING
-MICAELIS Sofa  and  Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.
-Product Dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21")
+MICAELIS Sofa and Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
 Size: Blue [NOT AVAILABLE]
 Features
 - Recliners
 - Sinious Spring and Webbing Suspension
 - Pillow Top Arms
 - 2.0 LB High Density Foam w/ Pocketed Coil Springs
-- FSC Certified
-Included items and dimensions:
+- FSC Certified Included items and dimensions:
 - Blue [NOT AVAILABLE] Sofa: color: Slate Blue; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional
 - Blue [NOT AVAILABLE] Loveseat: color: Slate Blue; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal
+Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
 Color: Slate Blue
 Weight: 372.58 lbs</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa  and  Loveseat Manual Blue [NOT AVAILABLE] | GOODDEGG</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual Blue [NOT AVAILABLE] | GOODDEGG</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Sofa + Loveseat Manual, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-SF-M, FM69007BL-LV-M</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="1" t="n">
         <v>372.58</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="Z3" s="1" t="n"/>
+      <c r="AA3" s="1" t="n"/>
+      <c r="AB3" s="1" t="n"/>
+      <c r="AC3" s="1" t="n">
         <v>58.1</v>
       </c>
     </row>

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,193 +420,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SKU</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Subcategory</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Subcategory</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>seo title(70char)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>seo title(70char)</t>
+          <t>seo description(160char)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>seo description(160char)</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Short Description</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Short Description</t>
+          <t>Short Description - Red Text</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Short Description - Red Text</t>
+          <t>Item Type</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Parts for Group Items</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Parts for Group Items</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>East(cost)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>East(cost)</t>
+          <t>EAST COST (Updated)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>EAST COST (Updated)</t>
+          <t>MSRP</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>MSRP</t>
+          <t>Weight (LB)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Weight (LB)</t>
+          <t>Product Dimension (Inch)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Product Dimension (Inch)</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Shipping Length (IN)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Shipping Length (IN)</t>
+          <t>Shipping Width (IN)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Shipping Width (IN)</t>
+          <t>Shipping Height (IN)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Shipping Height (IN)</t>
+          <t>Volume (CUFT)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Volume (CUFT)</t>
+          <t>Fixed tags</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Variable tags</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE]</t>
+          <t>FM69007BK-M-2PC</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>FM69007BK-M-2PC</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Sofa and Loveseat Manual</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa and Loveseat Manual</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.
@@ -625,45 +625,48 @@
 Weight: 372.58 lbs</t>
         </is>
       </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual Black [NOT AVAILABLE] | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa and Loveseat Manual Black [NOT AVAILABLE] | GOODDEGG</t>
+          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Sofa + Loveseat Manual, Black [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Sofa + Loveseat Manual, Black [NOT AVAILABLE]</t>
+          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM69007BK-SF-M, FM69007BK-LV-M</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>FM69007BK-SF-M, FM69007BK-LV-M</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
           <t>FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>0</v>
@@ -672,80 +675,82 @@
         <v>0</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="1" t="n">
         <v>372.58</v>
       </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+        </is>
+      </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
-          <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y2" s="1" t="n"/>
       <c r="Z2" s="1" t="n"/>
       <c r="AA2" s="1" t="n"/>
-      <c r="AB2" s="1" t="n"/>
-      <c r="AC2" s="1" t="n">
+      <c r="AB2" s="1" t="n">
         <v>58.1</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE</t>
+          <t>Slate Blue</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Slate Blue</t>
+          <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE]</t>
+          <t>FM69007BL-M-2PC</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>FM69007BL-M-2PC</t>
+          <t>Upholstery</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Upholstery</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MICAELIS Sofa and Loveseat Manual</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>MICAELIS Sofa and Loveseat Manual</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>FREE SHIPPING
 MICAELIS Sofa and Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.
@@ -764,45 +769,48 @@
 Weight: 372.58 lbs</t>
         </is>
       </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>MICAELIS Sofa and Loveseat Manual Blue [NOT AVAILABLE] | GOODDEGG</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa and Loveseat Manual Blue [NOT AVAILABLE] | GOODDEGG</t>
+          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS</t>
+          <t>Sofa + Loveseat Manual, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>Sofa + Loveseat Manual, Blue [NOT AVAILABLE]</t>
+          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>FM69007BL-SF-M, FM69007BL-LV-M</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>FM69007BL-SF-M, FM69007BL-LV-M</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
           <t>FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>0</v>
@@ -811,41 +819,48 @@
         <v>0</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="1" t="n">
         <v>372.58</v>
       </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+        </is>
+      </c>
       <c r="U3" s="1" t="inlineStr">
         <is>
-          <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
+          <t>Transitional</t>
         </is>
       </c>
       <c r="V3" s="1" t="inlineStr">
         <is>
-          <t>Transitional</t>
+          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
+          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr">
         <is>
-          <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
-        </is>
-      </c>
-      <c r="Y3" s="1" t="inlineStr">
-        <is>
           <t>MY</t>
         </is>
       </c>
+      <c r="Y3" s="1" t="n"/>
       <c r="Z3" s="1" t="n"/>
       <c r="AA3" s="1" t="n"/>
-      <c r="AB3" s="1" t="n"/>
-      <c r="AC3" s="1" t="n">
+      <c r="AB3" s="1" t="n">
         <v>58.1</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Upholstery, Motion, MICAELIS</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -608,21 +608,21 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")
-Size: Black [NOT AVAILABLE]
-Features
-- Recliners
-- Sinious Spring and Webbing Suspension
-- Pillow Top Arms
-- 2.0 LB High Density Foam w/ Pocketed Coil Springs
-- FSC Certified Included items and dimensions:
-- Black [NOT AVAILABLE] Sofa: color: Black; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional
-- Black [NOT AVAILABLE] Loveseat: color: Black; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Black
-Weight: 372.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
+Size: Black [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Recliners&lt;br&gt;
+- Sinious Spring and Webbing Suspension&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- 2.0 LB High Density Foam w/ Pocketed Coil Springs&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Black [NOT AVAILABLE] Sofa: color: Black; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional&lt;br&gt;
+- Black [NOT AVAILABLE] Loveseat: color: Black; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Black&lt;br&gt;
+Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -752,21 +752,21 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>FREE SHIPPING
-MICAELIS Sofa and Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")
-Size: Blue [NOT AVAILABLE]
-Features
-- Recliners
-- Sinious Spring and Webbing Suspension
-- Pillow Top Arms
-- 2.0 LB High Density Foam w/ Pocketed Coil Springs
-- FSC Certified Included items and dimensions:
-- Blue [NOT AVAILABLE] Sofa: color: Slate Blue; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional
-- Blue [NOT AVAILABLE] Loveseat: color: Slate Blue; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional
-Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.
-Color: Slate Blue
-Weight: 372.58 lbs</t>
+          <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
+MICAELIS Sofa and Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.&lt;br&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
+Size: Blue [NOT AVAILABLE]&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Recliners&lt;br&gt;
+- Sinious Spring and Webbing Suspension&lt;br&gt;
+- Pillow Top Arms&lt;br&gt;
+- 2.0 LB High Density Foam w/ Pocketed Coil Springs&lt;br&gt;
+- FSC Certified Included items and dimensions:&lt;br&gt;
+- Blue [NOT AVAILABLE] Sofa: color: Slate Blue; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional&lt;br&gt;
+- Blue [NOT AVAILABLE] Loveseat: color: Slate Blue; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
+&lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
+Color: Slate Blue&lt;br&gt;
+Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,6 +572,21 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Variable tags</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Product Category</t>
         </is>
       </c>
     </row>
@@ -715,7 +730,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
@@ -859,7 +889,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Upholstery, Motion, MICAELIS</t>
+          <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>GOODDEGG</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,18 +625,18 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")&lt;br&gt;
-Size: Black [NOT AVAILABLE]&lt;/p&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22") / 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
+Size: Black [NOT AVAILABLE]/Blue [NOT AVAILABLE]&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Recliners&lt;br&gt;
 - Sinious Spring and Webbing Suspension&lt;br&gt;
 - Pillow Top Arms&lt;br&gt;
 - 2.0 LB High Density Foam w/ Pocketed Coil Springs&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Black [NOT AVAILABLE] Sofa: color: Black; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional&lt;br&gt;
-- Black [NOT AVAILABLE] Loveseat: color: Black; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 19", SEAT DP: 22"); feature: Transitional&lt;/p&gt;
+- Black [NOT AVAILABLE] Sofa: color: Black or Slate Blue&lt;br&gt;
+- Black [NOT AVAILABLE] Loveseat: color: Black or Slate Blue&lt;/p&gt;
 &lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Slate Blue&lt;br&gt;
 Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -725,7 +725,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -783,19 +783,19 @@
       <c r="G3" s="1" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MICAELIS Sofa and Loveseat Manual offers a pulled-together look that makes the room feel ready to use and enjoy. As a upholstery motion, it is designed to coordinate with matching pieces. The Transitional character adds definition without feeling heavy. Crafted with Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal, then finished in Slate Blue tones to suit a range of interiors.&lt;br&gt;
-Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
-Size: Blue [NOT AVAILABLE]&lt;/p&gt;
+MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
+Product Dimensions: 75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22") / 75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")&lt;br&gt;
+Size: Black [NOT AVAILABLE]/Blue [NOT AVAILABLE]&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Recliners&lt;br&gt;
 - Sinious Spring and Webbing Suspension&lt;br&gt;
 - Pillow Top Arms&lt;br&gt;
 - 2.0 LB High Density Foam w/ Pocketed Coil Springs&lt;br&gt;
 - FSC Certified Included items and dimensions:&lt;br&gt;
-- Blue [NOT AVAILABLE] Sofa: color: Slate Blue; dimensions: 75" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional&lt;br&gt;
-- Blue [NOT AVAILABLE] Loveseat: color: Slate Blue; dimensions: 54.5" W x 36"D x 39.5" H (SEAT HT: 18.5", SEAT DP: 21"); feature: Transitional&lt;/p&gt;
+- Black [NOT AVAILABLE] Sofa: color: Black or Slate Blue&lt;br&gt;
+- Black [NOT AVAILABLE] Loveseat: color: Black or Slate Blue&lt;/p&gt;
 &lt;p&gt;Materials: Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal.&lt;br&gt;
-Color: Slate Blue&lt;br&gt;
+Color: Black or Slate Blue&lt;br&gt;
 Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -884,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa and Loveseat Manual Black [NOT AVAILABLE] | GOODDEGG</t>
+          <t>MICAELIS Sofa and Loveseat Manual | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Sofa and Loveseat Manual Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>MICAELIS Sofa and Loveseat Manual Blue [NOT AVAILABLE] | GOODDEGG</t>
+          <t>MICAELIS Sofa and Loveseat Manual | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>The MICAELIS Sofa and Loveseat Manual brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MICAELIS Sofa and Loveseat Manual Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">

--- a/FOA SETS/NOT_AVAILABLE_Set items.xlsx
+++ b/FOA SETS/NOT_AVAILABLE_Set items.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,208 +420,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subcategory</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>seo title(70char)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seo description(160char)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Short Description - Red Text</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Item Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Parts for Group Items</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Images</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Image src</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>combine image src</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>East(cost)</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EAST COST (Updated)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>MSRP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Weight (LB)</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Product Dimension (Inch)</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Shipping Length (IN)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Shipping Width (IN)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Shipping Height (IN)</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Volume (CUFT)</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Fixed tags</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Variable tags</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>micaelis-sofa-and-loveseat-manual</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-M-2PC</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
@@ -640,147 +660,158 @@
 Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual | GOODDEGG</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Sofa + Loveseat Manual, Black [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Black [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-SF-M, FM69007BK-LV-M</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>FM69007BK-M-1.jpg,FM69007BK-M-2.jpg</t>
         </is>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>FM69007BK-M-1.jpg,FM69007BK-M-2.jpg,FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="U2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="V2" s="1" t="n">
         <v>372.58</v>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 19", SEAT DP: 22")</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Transitional,Black,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="n"/>
-      <c r="Z2" s="1" t="n"/>
-      <c r="AA2" s="1" t="n"/>
-      <c r="AB2" s="1" t="n">
+      <c r="AB2" s="1" t="n"/>
+      <c r="AC2" s="1" t="n"/>
+      <c r="AD2" s="1" t="n"/>
+      <c r="AE2" s="1" t="n">
         <v>58.1</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>micaelis-sofa-and-loveseat-manual</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Slate Blue</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-M-2PC</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Upholstery</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 MICAELIS Sofa and Loveseat Manual is designed for everyday living, balancing comfort with a clean, finished look. Designed as a upholstery motion, it pairs easily with surrounding decor. Its Transitional styling keeps the room feeling polished yet comfortable. Built from Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal and finished in Black tones for a clean, cohesive look.&lt;br&gt;
@@ -799,110 +830,112 @@
 Weight: 372.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual | GOODDEGG</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>MICAELIS Sofa and Loveseat Manual Motion supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>MICAELIS</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Sofa + Loveseat Manual, Blue [NOT AVAILABLE]</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Blue [NOT AVAILABLE] NOT AVAILABLE</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-SF-M, FM69007BL-LV-M</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>FM69007BL-M-1.jpg,FM69007BL-M-2.jpg</t>
         </is>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="U3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="V3" s="1" t="n">
         <v>372.58</v>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>75"W X 36"D X 39.5"H (SEAT HT: 18.5", SEAT DP: 21")</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>Transitional</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="Z3" s="1" t="inlineStr">
         <is>
           <t>Transitional,Slate Blue,Leather Match, Fabric, Foam, Solid wood, Engineered Wood, Metal,Recliners,Sinious Spring and Webbing Suspension,Pillow Top Arms,2.0 LB High Density Foam w/ Pocketed Coil Springs,FSC Certified</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
+      <c r="AA3" s="1" t="inlineStr">
         <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="Y3" s="1" t="n"/>
-      <c r="Z3" s="1" t="n"/>
-      <c r="AA3" s="1" t="n"/>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3" s="1" t="n"/>
+      <c r="AC3" s="1" t="n"/>
+      <c r="AD3" s="1" t="n"/>
+      <c r="AE3" s="1" t="n">
         <v>58.1</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Upholstery, Motion, MICAELIS, LIVING ROOM FURNITURE</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>GOODDEGG</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>Furniture &gt; Sofas</t>
         </is>
